--- a/docs/ValueSet-ahip-yes-no-no-response.xlsx
+++ b/docs/ValueSet-ahip-yes-no-no-response.xlsx
@@ -94,7 +94,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc.
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -130,7 +131,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
